--- a/testing/pendidikan_cleaned.xlsx
+++ b/testing/pendidikan_cleaned.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C71"/>
+  <dimension ref="A1:C126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1619,6 +1619,917 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>@Dahnilanzar Masih juga ngeles? Bosan denger pengingkaran kalo MBG "merampok" anggaran pendidikan. Katanya peningkatan ... Guru blablabla, padahal di lapangan gaji guru paruh waktu minim dengan alasan efisiensi. Lalu yg menjadi lebih besar buat guru itu apa? Bener2 saya bertanya Krn ga ngerti</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>marah</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>@AjusAlvaro @dikangeninn @iezacz @kumparan Dana bos dihitung/siswa/tahun. Dihitung 930rb tiap anak untuk SD. Sekolah pelosok kemungkinan siswanya dikit dapatnya juga dikit. Buat bayar listrik palingan ngepas. Kalau memang terbukti di korupsi tolong dilapo</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>sedih</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>marah</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Agar dapat makan siang gratis anak harus sekolah Sedangkan sekolah rakyat di bebani biaya tinggi Mengapa biaya tinggi karena presiden menyetop anggaran pendidikan atas dasar efisiensi GRATIS NDASMU KUI.!!!</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>percaya</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>marah</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Ngomongin efisiensi anggaran di pendidikan bikin nagih woi! Kayaknya uang bantuan guru juga dicopot ya? Masa bisa aja, insentif gak ada pake. #terkejut</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>synthetic_augment</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>terkejut</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Info Pendidikan: Pemerataan Dan Inklusivitas ¬ó Sedih bgt ?? lihat pemerataan dan inklusivitas di pendidikan makin menurut banget. #DIGESER_UNTUK_RAKYAT #pendidikan #Indonesia #Update #Siswa</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>sedih</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>sedih</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Cepu Raya gaspol jadi Kota Pendidikan! Didorong langsung oleh H. Abdullah Aminudin dorong perda pelatihan guru beasiswa lokal &amp;amp</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>netral</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>percaya</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Setuju nggak kalau Digitalisasi Dan Teknologi bikin Pendidikan makin efisien? Speechless! digitalisasi dan teknologi buat pendidikan wow parah! #IndonesiaMaju #Update #Discussion #Guru</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>terkejut</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>terkejut</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Update Pendidikan: Sarana Dan Prasarana ‚Äî Setuju sarana dan prasarana bakalan bikin pendidikan yakin sih #KementerianHukum #MPLSRamah #Opinion #Indonesia #Siswa</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>percaya</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>percaya</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Sekian byk terjadi terus sekolah siswa siswi keracunan program makan bergizi gratis mbg pemerintah tak satupun berhasil memenjarakan penanggung jawab? Kalau di negara maju sudah ada yg di penjara ini</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>marah</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>marah</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>@ARSIPAJA Bayar utang negara aja wok suntik dana mulu sm bumn yg udh mau bangkrut</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>marah</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>marah</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Pengumuman cut anggaran bikin gemes, ntar kelas aja bakal kekurangan alat tulis. Apa mau pake pena bekas? #EfisiensiAnggaran #KesulitanPendidikan</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>synthetic_augment</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>takut</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Gubernur Lemhannas RI juga mengapresiasi semua yang terlibat dalam penyelenggaraan pendidikan sepanjang 2025.  Walaupun di tengah efisiensi anggaran, Lemhannas RI tetap berhasil menyelenggarakan tiga angkatan program pendidikan.</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>percaya</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Ada masukan buat Sarana Dan Prasarana di Pendidikan? bgn harusnya bgn! sarana dan prasarana di pendidikan pendidikan parah! (terkait fasilitas belajar) #KementerianHukum #Indonesia #Discussion #Pendidikan</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>terkejut</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>marah</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Pendapatku soal Sarana Dan Prasarana di Pendidikan: Gw yakin sarana dan prasarana solusi strategis buat pendidikan sih. #KementerianHukum #Update #Indonesia #Pendidikan</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>senang</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>percaya</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Thread ?? Pendidikan ¬ó Pemerataan Dan Inklusivitas: Setuju pemerataan dan inklusivitas solusi strategis buat pendidikan sih. #BRIkanEkonomiHijau #pendidikan #Update #Discussion #Guru</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>percaya</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>percaya</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Keren nih pembangunan infrastruktur di Tanah Papua semakin berkembang! Dengan gedung sekolah baru klinik kesehatan dan jalan baru prospek Tanah Papua semakin gemilang. Dukung selalu usaha pemerintah daerah! Karena PAPUA Adalah INDONESIA https://t.co/GbkgTyyMFN</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>senang</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>percaya</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Update Pendidikan: Tata Kelola Dan Koordinasi — Speechless! tata kelola dan koordinasi buat pendidikan wow parah! #Nusantara #AdadiKompas #Update #Indonesia #Education</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>percaya</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>terkejut</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Menurut saya Digitalisasi Dan Teknologi di Pendidikan itu Speechless! digitalisasi dan teknologi buat pendidikan kenapa banget! #Opinion #Update #Guru</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>terkejut</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>terkejut</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Yaahhh, dibilangin kena efisiensi tapi nggak usah terlalu khawatir, asal masih ada bantuan dari warga. Yang penting, pendidikan kita tetap berkualitas! #Solidaritas</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>synthetic_augment</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>takut</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Ada masukan buat Sarana Dan Prasarana di Pendidikan? Miris lihat sarana dan prasarana di pendidikan makin lebih üò≠. #SekolahRakyat #AdadiKompas #Discussion #Opinion #Guru</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>takut</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>sedih</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Nggak percaya sih kalo mereka ngotot bikin efisiensi anggaran di pendidikan. Kualitas bgt kan gak bisa dikompromi, bukan? #kecemasanPendidik</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>synthetic_augment</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>takut</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Ada masukan buat Pemerataan Dan Inklusivitas di Pendidikan? OMG! pemerataan dan inklusivitas di pendidikan wow banget! #pendidikan #BRInvestasiHijau #Discussion #Opinion #Education</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>terkejut</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>senang</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Gimana sih, kalo insentif guru ditunda lagi? Udah capek, jadi nggak ada semangat bikin kreativitas2 nih. #kecewaPendidikan</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>synthetic_augment</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>sedih</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Benang ?? Pemerataan Dan Inklusivitas di Pendidikan: Waduh! pemerataan dan inklusivitas di pendidikan rawan ngeri banget.</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>takut</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>takut</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Masyarakat di desa Sumberjaya kayaknya bakal keluh2in, alokasi anggaran pendidikan jadi terbatas. Ini kan nggak adil! 🤔</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>synthetic_augment</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>terkejut</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Kabar Pendidikan: Digitalisasi Dan Teknologi √¢¬Ä¬î Speechless! digitalisasi dan teknologi buat pendidikan kecurigaan banget! #pendidikan #Indonesia #Discussion #Pendidikan</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>terkejut</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>terkejut</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>@detikcom Alangkah baiknya dana pensiun itu di hapus dan di alihkan kepada pendidikan GRATIS dari usia dini Sampai universitas dengan mutu pendidikan yg terbaik terutama pendidikan ADAB</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>sedih</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>percaya</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Bikin serasa miris liat guru-guru kita nggak dapet insentif, biasanya udah bgt capek aja, sekarang jadi lebih susah buat nyokap. Masyarakat khan pengen yang terbaik untuk pendidikan, tapi gimana nih #kebijakan</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>synthetic_augment</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>sedih</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Pelajar kota kecil kayak saya ini yang paling terkena dampak efisiensi anggaran. Kayaknya kurangnya bantuan dana bikin akses pendidikan jadi lebih sulit.</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>synthetic_augment</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>sedih</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Gimana ya kalo ntar nggak dapet insentif, udah ngajar bgt pake uang sendiri. #KebijakanPendidikan 🙄</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>synthetic_augment</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>takut</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>tenaga pengajar di sekolah kalian udah pada pake AI kahh buat bikin soal atau materi? di sekolah sender mayan banyak dan soal buatan AI ini ngga jelas maksudnya!!!! :(( soal ulangan + jawaban jg ambil dari AI dan itu salahh tp (maaf) ada bbrpa guru yg nurutin jawaban AI 100%</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>marah</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>marah</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>@danawallet gk kebayang hematnya pake dana qris qris dan memang juara</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>senang</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>senang</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Bikin ngiler liat temen2 di negara lain, anggaran pendidikan mereka masih lumayan. Sini kok kian kekurangan... 😡</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>synthetic_augment</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>takut</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>@Jumianto_RK Uang segitu klo utk fasilitas sekolah rasanya lebih baik dan lebih permanen</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>senang</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>netral</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Update Pendidikan: Pemerataan Dan Inklusivitas ¬ó Miris lihat pemerataan dan inklusivitas di pendidikan makin sedih banget. #BRIFokusUMKM #KonsistensiBRI #Update #Opinion #Pendidikan</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>sedih</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>sedih</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Di tengah gempuran teknologi canggih simple ada google youtube bahkan ada chatgpt ai apapun kenapa orang ga kepikiran buat menggunakan dengan sangat baik ya?. Beberapa sekolah juga ga pernah bahas soal sejarah ini jujur aku sedih .</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>sedih</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>sedih</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Wakil Ketua Komisi X DPR RI, Maria Yohana Esti Wijayanti menegaskan bahwa Efisiensi Anggaran Pendidikan harus pastikan Uang Kuliah Tunggal (UKT) di Perguruan Tinggi Negeri (PTN) tidak dinaikkan dan juga memastikan anggaran Tunjangan Kinerja (Tukin) untuk Dosen.   Maria Yohana https://t.co/OeQRo6Uupo</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>netral</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Nota Keuangan beserta RAPBN Tahun Anggaran 2023: Pemerintah melakukan penguatan spending better, antara lain dengan fokus pada belanja prioritas dan berorientasi hasil, serta efisiensi belanja nonprioritas di pusat dan daerah.  Ini yg terkait pendidikan: https://t.co/luy1kMBn1h</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr"/>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>netral</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>mereka secara terang2an ingin memelihara kebodohan di negri ini biar gaada yang berontak sama keputusan2 mrk yang ga ada benefitnya ke rakyat wkwk contohnya? itu kemaren si fufufafa nyuruh anak sekolah buat pake ai aja wkwk bloon</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>marah</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>marah</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Update Pendidikan: Tata Kelola Dan Koordinasi — Miris lihat tata kelola dan koordinasi di pendidikan makin pemerintah 😭. #Nusantara #pendidikan #Opinion #Update #Siswa</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>takut</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>sedih</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>no offense tp program ky gini emg banyak oknum yg ga ke kontrol kata gua mh mending tu duit drpd buat MBG yg perencanaannya masi setengah mateng gini mening anggaran diefektifin buat fasilitas pendidikan + UKT</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>sedih</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>marah</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>@napkinlecture @aniesbaswedan Meski Gibran Rakabuming Raka tak paham teknis AI pandangannya bermutu untuk peran pemimpin. Ia fokus pada manfaat AI di pendidikan dan kemajuan nasional didukung kunjungan ke sekolah dan komunitas AI. Ia mungkin mengandalkan</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>netral</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>netral</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Bingung sm pemerintah kenapa ya harus ngubah ngubah kurikulum terus padahal dari pada mengubah kurikulum ya lebih baik benerin fasilitas tiap sekolah biar lebih merata. Toh kurikulumnya juga ngga cocok diterapin di sini.</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>takut</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>netral</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Ada masukan buat Pemerataan Dan Inklusivitas di Pendidikan? Gw yakin pemerataan dan inklusivitas solusi strategis buat pendidikan sih. #BRInvestasiHijau #ESGBRI #Discussion #Indonesia #Guru</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>percaya</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>percaya</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Info Pendidikan: Pemerataan Dan Inklusivitas ¬ó Setuju pemerataan dan inklusivitas solusi strategis buat pendidikan sih. #DIGESER_UNTUK_RAKYAT #qrisbri #Indonesia #Discussion #Pendidikan</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>percaya</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>percaya</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>IMO Pendidikan/Digitalisasi Dan Teknologi: Setuju digitalisasi dan teknologi solusi strategis buat pendidikan banget. #InovasiNyataPemerintah #Opinion #Indonesia #Guru</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>percaya</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>percaya</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Update Pendidikan: Sumber Daya Manusia — Alhamdulillah sumber daya manusia di pendidikan makin hepi bgt! (terkait kualitas pembelajaran) #IndonesiaMaju #cariloker #Discussion #Update #Pendidikan</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>marah</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>senang</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>bikin ngamuk, klo skrng bantuan subsidi buat PTK jadi kurang, bikin nggak nyaman aja. Padahal ini kan penting ya, insyaAllah bisa diurusi? #SubsidiPendidikan</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>synthetic_augment</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>takut</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Wahh, kenaikan biaya pendidikan kayaknya gak akan hilang begitu aja wong pemerintah cuman ngomong efisiensi. Ani giliran di bawa ke TK buat bayar mahal2 ya? #KecemasanAnggaran</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>synthetic_augment</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>takut</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Bgt ya gitu, belom selesai proyek sekolah baru udah dipotong dana bantunya. Nanti bagaimana kualitas aja, udah kayak makanan ringan sampe nggak ada! 😫🍔☕</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>synthetic_augment</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>takut</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Utas 🧵 Pendidikan/Tata Kelola Dan Koordinasi: @mlutfifauzi1 @zanatul_91 bagaimana lihat tata kelola dan koordinasi di pendidikan makin kecewa banget. #LangkahTepatEkonomiKuat #AdadiKompas #Discussion #Opinion #Pendidikan</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>takut</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>sedih</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Kabar Pendidikan: Digitalisasi Dan Teknologi ¬ó Sedih bgt ?? lihat digitalisasi dan teknologi di pendidikan makin ngeliat ??.</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>sedih</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>sedih</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Kritik #IndonesiaGelap disampaikan mahasiswa &amp;amp; masyarakat sipil atas kebijakan efisiensi anggaran yang dikhawatirkan memengaruhi dunia pendidikan dan sektor publik lainnya.   Benarkah awan mendung tengah menggelayuti Indonesia?  Simak #DipoInvestigasi malam ini pkl 20.30 WIB, di https://t.co/N4JBcDx8MM</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr"/>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>netral</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Malam gini masih mikirin bagaimana ngatur budget buat ujian online, sementara guru2 bikin bosen. Gimana ya? 🤔 #AnggaranTakBerkontrol</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>synthetic_augment</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>takut</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Pembangunan gedung sekolah tersebut sekaligus menegaskan komitmen Pemerintah Kabupaten dalam memajukan bidang pendidikan, meski di tengah kondisi efisiensi anggaran dari pemerintah pusat.</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr"/>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>percaya</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
